--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.09629159519286</v>
+        <v>6.19064738421884</v>
       </c>
       <c r="D2" t="n">
-        <v>38.7302983274934</v>
+        <v>6.293673478217678</v>
       </c>
       <c r="E2" t="n">
-        <v>24.37799110813289</v>
+        <v>3.961423555071593</v>
       </c>
       <c r="F2" t="n">
-        <v>24.64078878479917</v>
+        <v>4.004128177529865</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>87.73886521766343</v>
+        <v>14.25756559787031</v>
       </c>
       <c r="D3" t="n">
-        <v>88.24092456800054</v>
+        <v>14.33915024230009</v>
       </c>
       <c r="E3" t="n">
-        <v>24.37799110813289</v>
+        <v>3.961423555071593</v>
       </c>
       <c r="F3" t="n">
-        <v>24.64078878479917</v>
+        <v>4.004128177529865</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.67165172163561</v>
+        <v>3.684143404765786</v>
       </c>
       <c r="D4" t="n">
-        <v>22.33256758370911</v>
+        <v>3.629042232352731</v>
       </c>
       <c r="E4" t="n">
-        <v>24.37799110813289</v>
+        <v>3.961423555071593</v>
       </c>
       <c r="F4" t="n">
-        <v>24.64078878479917</v>
+        <v>4.004128177529865</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.18345932541636</v>
+        <v>6.529812140380159</v>
       </c>
       <c r="D5" t="n">
-        <v>39.83655544000279</v>
+        <v>6.473440259000454</v>
       </c>
       <c r="E5" t="n">
-        <v>24.37799110813289</v>
+        <v>3.961423555071593</v>
       </c>
       <c r="F5" t="n">
-        <v>24.64078878479917</v>
+        <v>4.004128177529865</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
